--- a/pvmd/utils/settings.xlsx
+++ b/pvmd/utils/settings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\PhD Youri Blom\PVMD_TOOLBOX\TOOLBOX_Develop\pvmd\utils\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\PhD Youri Blom\PVMD_TOOLBOX\TOOLBOX_develop\pvmd\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2BD5FB-4B37-4F62-AF7B-EE2CB27A5161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772B37A8-BDC0-4CAD-9C96-0CB571B8C142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="5" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="136">
   <si>
     <t>material</t>
   </si>
@@ -451,6 +451,12 @@
   </si>
   <si>
     <t>E</t>
+  </si>
+  <si>
+    <t>SolidAngleSun</t>
+  </si>
+  <si>
+    <t>[SR]</t>
   </si>
 </sst>
 </file>
@@ -795,7 +801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14E82549-7F0C-411E-A3D7-D2E22A6A0F58}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
@@ -898,6 +904,17 @@
       </c>
       <c r="C9" t="s">
         <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="5">
+        <v>6.7700000000000006E-5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
